--- a/data/availability/projects/misr-italia-properties/vinci.xlsx
+++ b/data/availability/projects/misr-italia-properties/vinci.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>delivery_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for vinci</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -587,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -604,7 +614,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sky Villa</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -637,7 +647,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +697,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +747,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +797,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Aug 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -887,7 +897,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2027/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1009,7 +1019,6 @@
       <c r="G2" t="n">
         <v>172</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1020,7 +1029,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1081,7 +1090,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1103,7 +1112,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sky Villa</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1127,7 +1136,6 @@
       <c r="G4" t="n">
         <v>318</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1138,7 +1146,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1199,7 +1207,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1245,7 +1253,6 @@
       <c r="G6" t="n">
         <v>156</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1256,7 +1263,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1302,7 +1309,6 @@
       <c r="G7" t="n">
         <v>255</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1313,7 +1319,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Aug 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1359,7 +1365,6 @@
       <c r="G8" t="n">
         <v>316</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1416,7 +1421,6 @@
       <c r="G9" t="n">
         <v>510</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1427,7 +1431,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2027/2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
